--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_ZALGIRIS KAUNAS.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_ZALGIRIS KAUNAS.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>76.3133</v>
+        <v>68.0891</v>
       </c>
       <c r="E2" t="n">
-        <v>59.9948</v>
+        <v>58.6907</v>
       </c>
       <c r="F2" t="n">
-        <v>16.3184</v>
+        <v>9.398300000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>6.8171</v>
+        <v>91.6575</v>
       </c>
       <c r="H2" t="n">
-        <v>12.991</v>
+        <v>33.9692</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.174099999999999</v>
+        <v>57.6891</v>
       </c>
       <c r="J2" t="n">
-        <v>44.6003</v>
+        <v>126.7929</v>
       </c>
       <c r="K2" t="n">
-        <v>35.1659</v>
+        <v>50.4783</v>
       </c>
       <c r="L2" t="n">
-        <v>9.434100000000001</v>
+        <v>76.3152</v>
       </c>
       <c r="M2" t="n">
-        <v>-37.7832</v>
+        <v>-35.1355</v>
       </c>
       <c r="N2" t="n">
-        <v>-22.1752</v>
+        <v>-16.5093</v>
       </c>
       <c r="O2" t="n">
-        <v>-15.6087</v>
+        <v>-18.6257</v>
       </c>
       <c r="P2" t="n">
-        <v>-9.2782</v>
+        <v>-62.3954</v>
       </c>
       <c r="Q2" t="n">
-        <v>-65.64279999999999</v>
+        <v>-128.7333</v>
       </c>
       <c r="R2" t="n">
-        <v>56.3649</v>
+        <v>66.33879999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>58.8466</v>
+        <v>0.4180999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>42.2999</v>
+        <v>-1.6949</v>
       </c>
       <c r="U2" t="n">
-        <v>16.5464</v>
+        <v>2.113</v>
       </c>
       <c r="V2" t="n">
-        <v>19.9282</v>
+        <v>38.4079</v>
       </c>
       <c r="W2" t="n">
-        <v>38.7372</v>
+        <v>62.3254</v>
       </c>
       <c r="X2" t="n">
-        <v>-18.809</v>
+        <v>-23.9175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>37.15009999999999</v>
+        <v>40.8924</v>
       </c>
       <c r="E3" t="n">
-        <v>36.5676</v>
+        <v>31.7014</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5829000000000009</v>
+        <v>9.191299999999998</v>
       </c>
       <c r="G3" t="n">
-        <v>91.6575</v>
+        <v>6.8171</v>
       </c>
       <c r="H3" t="n">
-        <v>33.9692</v>
+        <v>12.991</v>
       </c>
       <c r="I3" t="n">
-        <v>57.6891</v>
+        <v>-6.174099999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>126.7929</v>
+        <v>44.6003</v>
       </c>
       <c r="K3" t="n">
-        <v>50.4783</v>
+        <v>35.1659</v>
       </c>
       <c r="L3" t="n">
-        <v>76.3152</v>
+        <v>9.434100000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-35.1355</v>
+        <v>-37.7832</v>
       </c>
       <c r="N3" t="n">
-        <v>-16.5093</v>
+        <v>-22.1752</v>
       </c>
       <c r="O3" t="n">
-        <v>-18.6257</v>
+        <v>-15.6087</v>
       </c>
       <c r="P3" t="n">
-        <v>-62.3954</v>
+        <v>-9.2782</v>
       </c>
       <c r="Q3" t="n">
-        <v>-128.7333</v>
+        <v>-65.64279999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>66.33879999999999</v>
+        <v>56.3649</v>
       </c>
       <c r="S3" t="n">
-        <v>-30.5208</v>
+        <v>23.4261</v>
       </c>
       <c r="T3" t="n">
-        <v>-23.8185</v>
+        <v>14.0068</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.702400000000001</v>
+        <v>9.418799999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>38.4079</v>
+        <v>19.9282</v>
       </c>
       <c r="W3" t="n">
-        <v>62.3254</v>
+        <v>38.7372</v>
       </c>
       <c r="X3" t="n">
-        <v>-23.9175</v>
+        <v>-18.809</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>27.7708</v>
+        <v>28.6977</v>
       </c>
       <c r="E4" t="n">
-        <v>23.2487</v>
+        <v>30.7776</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5217</v>
+        <v>-2.080000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2083</v>
+        <v>15.7911</v>
       </c>
       <c r="H4" t="n">
-        <v>15.7322</v>
+        <v>4.079700000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5241000000000011</v>
+        <v>11.7116</v>
       </c>
       <c r="J4" t="n">
-        <v>41.8085</v>
+        <v>42.7582</v>
       </c>
       <c r="K4" t="n">
-        <v>31.8896</v>
+        <v>15.7551</v>
       </c>
       <c r="L4" t="n">
-        <v>9.918200000000001</v>
+        <v>27.003</v>
       </c>
       <c r="M4" t="n">
-        <v>-26.6002</v>
+        <v>-26.9674</v>
       </c>
       <c r="N4" t="n">
-        <v>-16.1577</v>
+        <v>-11.6754</v>
       </c>
       <c r="O4" t="n">
-        <v>-10.4426</v>
+        <v>-15.2915</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4640000000000004</v>
+        <v>23.8915</v>
       </c>
       <c r="Q4" t="n">
-        <v>-53.8133</v>
+        <v>-16.4688</v>
       </c>
       <c r="R4" t="n">
-        <v>54.2773</v>
+        <v>40.36</v>
       </c>
       <c r="S4" t="n">
-        <v>21.8589</v>
+        <v>1.7715</v>
       </c>
       <c r="T4" t="n">
-        <v>16.0511</v>
+        <v>-1.4402</v>
       </c>
       <c r="U4" t="n">
-        <v>5.8084</v>
+        <v>3.2117</v>
       </c>
       <c r="V4" t="n">
-        <v>-9.7606</v>
+        <v>-12.7557</v>
       </c>
       <c r="W4" t="n">
-        <v>19.2025</v>
+        <v>5.9282</v>
       </c>
       <c r="X4" t="n">
-        <v>-28.9631</v>
+        <v>-18.6839</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>24.6728</v>
+        <v>22.5307</v>
       </c>
       <c r="E5" t="n">
-        <v>20.624</v>
+        <v>25.94</v>
       </c>
       <c r="F5" t="n">
-        <v>4.049</v>
+        <v>-3.4094</v>
       </c>
       <c r="G5" t="n">
-        <v>13.8071</v>
+        <v>-7.5318</v>
       </c>
       <c r="H5" t="n">
-        <v>14.2305</v>
+        <v>-15.205</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4234999999999998</v>
+        <v>7.6731</v>
       </c>
       <c r="J5" t="n">
-        <v>22.2731</v>
+        <v>17.9875</v>
       </c>
       <c r="K5" t="n">
-        <v>17.7462</v>
+        <v>0.5770999999999995</v>
       </c>
       <c r="L5" t="n">
-        <v>4.5267</v>
+        <v>17.4104</v>
       </c>
       <c r="M5" t="n">
-        <v>-8.4663</v>
+        <v>-25.5188</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.5158</v>
+        <v>-15.7823</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.9506</v>
+        <v>-9.7371</v>
       </c>
       <c r="P5" t="n">
-        <v>5.1031</v>
+        <v>20.412</v>
       </c>
       <c r="Q5" t="n">
-        <v>-16.2371</v>
+        <v>-23.4278</v>
       </c>
       <c r="R5" t="n">
-        <v>21.3403</v>
+        <v>43.8394</v>
       </c>
       <c r="S5" t="n">
-        <v>17.4019</v>
+        <v>2.3189</v>
       </c>
       <c r="T5" t="n">
-        <v>14.7334</v>
+        <v>4.7341</v>
       </c>
       <c r="U5" t="n">
-        <v>2.6692</v>
+        <v>-2.4148</v>
       </c>
       <c r="V5" t="n">
-        <v>-11.6388</v>
+        <v>7.331799999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1455999999999997</v>
+        <v>26.6458</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.4932</v>
+        <v>-19.314</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>21.8107</v>
+        <v>16.6858</v>
       </c>
       <c r="E6" t="n">
-        <v>25.1633</v>
+        <v>12.8843</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.352700000000001</v>
+        <v>3.801</v>
       </c>
       <c r="G6" t="n">
-        <v>15.7911</v>
+        <v>15.2083</v>
       </c>
       <c r="H6" t="n">
-        <v>4.079700000000001</v>
+        <v>15.7322</v>
       </c>
       <c r="I6" t="n">
-        <v>11.7116</v>
+        <v>-0.5241000000000011</v>
       </c>
       <c r="J6" t="n">
-        <v>42.7582</v>
+        <v>41.8085</v>
       </c>
       <c r="K6" t="n">
-        <v>15.7551</v>
+        <v>31.8896</v>
       </c>
       <c r="L6" t="n">
-        <v>27.003</v>
+        <v>9.918200000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-26.9674</v>
+        <v>-26.6002</v>
       </c>
       <c r="N6" t="n">
-        <v>-11.6754</v>
+        <v>-16.1577</v>
       </c>
       <c r="O6" t="n">
-        <v>-15.2915</v>
+        <v>-10.4426</v>
       </c>
       <c r="P6" t="n">
-        <v>23.8915</v>
+        <v>0.4640000000000004</v>
       </c>
       <c r="Q6" t="n">
-        <v>-16.4688</v>
+        <v>-53.8133</v>
       </c>
       <c r="R6" t="n">
-        <v>40.36</v>
+        <v>54.2773</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.1154</v>
+        <v>10.7742</v>
       </c>
       <c r="T6" t="n">
-        <v>-7.0545</v>
+        <v>5.6866</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9388</v>
+        <v>5.0876</v>
       </c>
       <c r="V6" t="n">
-        <v>-12.7557</v>
+        <v>-9.7606</v>
       </c>
       <c r="W6" t="n">
-        <v>5.9282</v>
+        <v>19.2025</v>
       </c>
       <c r="X6" t="n">
-        <v>-18.6839</v>
+        <v>-28.9631</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>14.0317</v>
+        <v>16.2758</v>
       </c>
       <c r="E7" t="n">
-        <v>23.0383</v>
+        <v>13.1749</v>
       </c>
       <c r="F7" t="n">
-        <v>-9.006399999999999</v>
+        <v>3.100899999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-7.5318</v>
+        <v>29.5919</v>
       </c>
       <c r="H7" t="n">
-        <v>-15.205</v>
+        <v>-5.7965</v>
       </c>
       <c r="I7" t="n">
-        <v>7.6731</v>
+        <v>35.3887</v>
       </c>
       <c r="J7" t="n">
-        <v>17.9875</v>
+        <v>55.7768</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5770999999999995</v>
+        <v>13.0231</v>
       </c>
       <c r="L7" t="n">
-        <v>17.4104</v>
+        <v>42.7534</v>
       </c>
       <c r="M7" t="n">
-        <v>-25.5188</v>
+        <v>-26.1845</v>
       </c>
       <c r="N7" t="n">
-        <v>-15.7823</v>
+        <v>-18.8198</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.7371</v>
+        <v>-7.3651</v>
       </c>
       <c r="P7" t="n">
-        <v>20.412</v>
+        <v>-19.9479</v>
       </c>
       <c r="Q7" t="n">
-        <v>-23.4278</v>
+        <v>-60.772</v>
       </c>
       <c r="R7" t="n">
-        <v>43.8394</v>
+        <v>40.8239</v>
       </c>
       <c r="S7" t="n">
-        <v>-6.1796</v>
+        <v>3.6055</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8328</v>
+        <v>0.5263999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-8.012</v>
+        <v>3.0788</v>
       </c>
       <c r="V7" t="n">
-        <v>7.331799999999999</v>
+        <v>3.0263</v>
       </c>
       <c r="W7" t="n">
-        <v>26.6458</v>
+        <v>17.6428</v>
       </c>
       <c r="X7" t="n">
-        <v>-19.314</v>
+        <v>-14.6165</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>6.095699999999999</v>
+        <v>15.7188</v>
       </c>
       <c r="E8" t="n">
-        <v>11.4079</v>
+        <v>11.4745</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.312</v>
+        <v>4.2437</v>
       </c>
       <c r="G8" t="n">
-        <v>-15.0405</v>
+        <v>13.8071</v>
       </c>
       <c r="H8" t="n">
-        <v>-21.1024</v>
+        <v>14.2305</v>
       </c>
       <c r="I8" t="n">
-        <v>6.0617</v>
+        <v>-0.4234999999999998</v>
       </c>
       <c r="J8" t="n">
-        <v>9.9838</v>
+        <v>22.2731</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.017300000000001</v>
+        <v>17.7462</v>
       </c>
       <c r="L8" t="n">
-        <v>19.0013</v>
+        <v>4.5267</v>
       </c>
       <c r="M8" t="n">
-        <v>-25.0244</v>
+        <v>-8.4663</v>
       </c>
       <c r="N8" t="n">
-        <v>-12.0847</v>
+        <v>-3.5158</v>
       </c>
       <c r="O8" t="n">
-        <v>-12.9393</v>
+        <v>-4.9506</v>
       </c>
       <c r="P8" t="n">
-        <v>14.6131</v>
+        <v>5.1031</v>
       </c>
       <c r="Q8" t="n">
-        <v>-29.4583</v>
+        <v>-16.2371</v>
       </c>
       <c r="R8" t="n">
-        <v>44.0714</v>
+        <v>21.3403</v>
       </c>
       <c r="S8" t="n">
-        <v>17.6228</v>
+        <v>8.4475</v>
       </c>
       <c r="T8" t="n">
-        <v>12.9558</v>
+        <v>5.584000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>4.6673</v>
+        <v>2.8639</v>
       </c>
       <c r="V8" t="n">
-        <v>-11.0995</v>
+        <v>-11.6388</v>
       </c>
       <c r="W8" t="n">
-        <v>17.9264</v>
+        <v>-0.1455999999999997</v>
       </c>
       <c r="X8" t="n">
-        <v>-29.0259</v>
+        <v>-11.4932</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>3.5402</v>
+        <v>2.6009</v>
       </c>
       <c r="E9" t="n">
-        <v>5.040300000000002</v>
+        <v>6.6738</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.500300000000001</v>
+        <v>-4.072699999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>29.5919</v>
+        <v>-15.0405</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.7965</v>
+        <v>-21.1024</v>
       </c>
       <c r="I9" t="n">
-        <v>35.3887</v>
+        <v>6.0617</v>
       </c>
       <c r="J9" t="n">
-        <v>55.7768</v>
+        <v>9.9838</v>
       </c>
       <c r="K9" t="n">
-        <v>13.0231</v>
+        <v>-9.017300000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>42.7534</v>
+        <v>19.0013</v>
       </c>
       <c r="M9" t="n">
-        <v>-26.1845</v>
+        <v>-25.0244</v>
       </c>
       <c r="N9" t="n">
-        <v>-18.8198</v>
+        <v>-12.0847</v>
       </c>
       <c r="O9" t="n">
-        <v>-7.3651</v>
+        <v>-12.9393</v>
       </c>
       <c r="P9" t="n">
-        <v>-19.9479</v>
+        <v>14.6131</v>
       </c>
       <c r="Q9" t="n">
-        <v>-60.772</v>
+        <v>-29.4583</v>
       </c>
       <c r="R9" t="n">
-        <v>40.8239</v>
+        <v>44.0714</v>
       </c>
       <c r="S9" t="n">
-        <v>-9.1303</v>
+        <v>14.1281</v>
       </c>
       <c r="T9" t="n">
-        <v>-7.6082</v>
+        <v>8.221500000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5225</v>
+        <v>5.9066</v>
       </c>
       <c r="V9" t="n">
-        <v>3.0263</v>
+        <v>-11.0995</v>
       </c>
       <c r="W9" t="n">
-        <v>17.6428</v>
+        <v>17.9264</v>
       </c>
       <c r="X9" t="n">
-        <v>-14.6165</v>
+        <v>-29.0259</v>
       </c>
     </row>
     <row r="10">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. MIKALAUSKAS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1959</v>
+        <v>-0.1240000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.613</v>
+        <v>-4.009</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5829</v>
+        <v>3.8848</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8622</v>
+        <v>0.2531</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8187</v>
+        <v>-0.7674999999999998</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04349999999999987</v>
+        <v>1.020899999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1441</v>
+        <v>7.1725</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4655</v>
+        <v>3.3721</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3212999999999999</v>
+        <v>3.8004</v>
       </c>
       <c r="M11" t="n">
-        <v>0.718</v>
+        <v>-6.9192</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3533</v>
+        <v>-4.1398</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3648</v>
+        <v>-2.7794</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4639</v>
+        <v>2.0875</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3917</v>
+        <v>-12.0617</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278999999999999</v>
+        <v>14.1493</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9137</v>
+        <v>-0.5731999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3655</v>
+        <v>0.5966000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5483</v>
+        <v>-1.1696</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.6805</v>
+        <v>-1.8919</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6805</v>
+        <v>-2.1755</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>K. MIKALAUSKAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.735600000000001</v>
+        <v>-1.2194</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.233099999999999</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4977</v>
+        <v>-1.3141</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2531</v>
+        <v>1.8622</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7674999999999998</v>
+        <v>1.8187</v>
       </c>
       <c r="I12" t="n">
-        <v>1.020899999999999</v>
+        <v>0.04349999999999987</v>
       </c>
       <c r="J12" t="n">
-        <v>7.1725</v>
+        <v>1.1441</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3721</v>
+        <v>1.4655</v>
       </c>
       <c r="L12" t="n">
-        <v>3.8004</v>
+        <v>-0.3212999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.9192</v>
+        <v>0.718</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.1398</v>
+        <v>0.3533</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.7794</v>
+        <v>0.3648</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0875</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.0617</v>
+        <v>-1.3917</v>
       </c>
       <c r="R12" t="n">
-        <v>14.1493</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.184600000000001</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3724000000000001</v>
+        <v>0.3422</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.557</v>
+        <v>-0.2793</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8919</v>
+        <v>-2.6805</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1755</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.621299999999999</v>
+        <v>-1.912500000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6364</v>
+        <v>-2.0284</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01509999999999984</v>
+        <v>0.1157</v>
       </c>
       <c r="G13" t="n">
         <v>-3.265</v>
@@ -1468,13 +1468,13 @@
         <v>3.2477</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5932999999999999</v>
+        <v>1.1153</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5694</v>
+        <v>1.0387</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.02430000000000002</v>
+        <v>0.0766</v>
       </c>
       <c r="V13" t="n">
         <v>1.8608</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.2415</v>
+        <v>-3.266900000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.1825</v>
+        <v>-5.2859</v>
       </c>
       <c r="F14" t="n">
-        <v>9.9407</v>
+        <v>2.018999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.490499999999999</v>
+        <v>5.292700000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8555000000000004</v>
+        <v>-1.740500000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.346200000000001</v>
+        <v>7.033300000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.037999999999999</v>
+        <v>28.4136</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4639</v>
+        <v>6.610699999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-9.5016</v>
+        <v>21.8031</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4526</v>
+        <v>-23.1207</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.6083</v>
+        <v>-8.350899999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1558</v>
+        <v>-14.7694</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2319999999999995</v>
+        <v>-3.9433</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.2524</v>
+        <v>-45.6946</v>
       </c>
       <c r="R14" t="n">
-        <v>19.4843</v>
+        <v>41.7517</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.7431</v>
+        <v>-1.0538</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.0036</v>
+        <v>-3.3619</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.74</v>
+        <v>2.3084</v>
       </c>
       <c r="V14" t="n">
-        <v>2.7601</v>
+        <v>-3.563200000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>7.1111</v>
+        <v>15.3565</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.351</v>
+        <v>-18.9197</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-20.1084</v>
+        <v>-6.6971</v>
       </c>
       <c r="E15" t="n">
-        <v>-18.673</v>
+        <v>-19.7673</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4358</v>
+        <v>13.07</v>
       </c>
       <c r="G15" t="n">
-        <v>5.292700000000001</v>
+        <v>-7.490499999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.740500000000001</v>
+        <v>0.8555000000000004</v>
       </c>
       <c r="I15" t="n">
-        <v>7.033300000000001</v>
+        <v>-8.346200000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>28.4136</v>
+        <v>-6.037999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>6.610699999999999</v>
+        <v>3.4639</v>
       </c>
       <c r="L15" t="n">
-        <v>21.8031</v>
+        <v>-9.5016</v>
       </c>
       <c r="M15" t="n">
-        <v>-23.1207</v>
+        <v>-1.4526</v>
       </c>
       <c r="N15" t="n">
-        <v>-8.350899999999999</v>
+        <v>-2.6083</v>
       </c>
       <c r="O15" t="n">
-        <v>-14.7694</v>
+        <v>1.1558</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.9433</v>
+        <v>0.2319999999999995</v>
       </c>
       <c r="Q15" t="n">
-        <v>-45.6946</v>
+        <v>-19.2524</v>
       </c>
       <c r="R15" t="n">
-        <v>41.7517</v>
+        <v>19.4843</v>
       </c>
       <c r="S15" t="n">
-        <v>-17.8951</v>
+        <v>-2.1985</v>
       </c>
       <c r="T15" t="n">
-        <v>-16.7489</v>
+        <v>-1.5885</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.1463</v>
+        <v>-0.6103</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.563200000000001</v>
+        <v>2.7601</v>
       </c>
       <c r="W15" t="n">
-        <v>15.3565</v>
+        <v>7.1111</v>
       </c>
       <c r="X15" t="n">
-        <v>-18.9197</v>
+        <v>-4.351</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>-26.6402</v>
+        <v>-18.8644</v>
       </c>
       <c r="E16" t="n">
-        <v>-32.6077</v>
+        <v>-28.3539</v>
       </c>
       <c r="F16" t="n">
-        <v>5.9678</v>
+        <v>9.489699999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-31.1606</v>
@@ -1702,13 +1702,13 @@
         <v>35.4895</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.1514</v>
+        <v>2.6248</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.636200000000001</v>
+        <v>-0.3827999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5147</v>
+        <v>3.0071</v>
       </c>
       <c r="V16" t="n">
         <v>-6.1011</v>
@@ -1735,13 +1735,13 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>142.0945</v>
+        <v>179.659</v>
       </c>
       <c r="E17" t="n">
-        <v>121.3913</v>
+        <v>132.2195</v>
       </c>
       <c r="F17" t="n">
-        <v>20.7032</v>
+        <v>47.43819999999999</v>
       </c>
       <c r="G17" t="n">
         <v>116.0447</v>
@@ -1771,22 +1771,22 @@
         <v>-116.6575</v>
       </c>
       <c r="P17" t="n">
-        <v>-15.07570000000002</v>
+        <v>-15.07570000000001</v>
       </c>
       <c r="Q17" t="n">
         <v>-497.5411999999999</v>
       </c>
       <c r="R17" t="n">
-        <v>482.4664</v>
+        <v>482.4664000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>27.30290000000001</v>
+        <v>64.8673</v>
       </c>
       <c r="T17" t="n">
-        <v>21.4406</v>
+        <v>32.2686</v>
       </c>
       <c r="U17" t="n">
-        <v>5.862599999999996</v>
+        <v>32.5985</v>
       </c>
       <c r="V17" t="n">
         <v>13.8238</v>
